--- a/Excel Files/point_load.xlsx
+++ b/Excel Files/point_load.xlsx
@@ -19,7 +19,7 @@
     <x:t>Tipi</x:t>
   </x:si>
   <x:si>
-    <x:t>Kapladığı Alan (m2)</x:t>
+    <x:t>Ortalama Kapladığı Alan (m2)</x:t>
   </x:si>
   <x:si>
     <x:t>Tüketim Sınıfı</x:t>
@@ -37,7 +37,7 @@
     <x:t>Anaokulu</x:t>
   </x:si>
   <x:si>
-    <x:t>2800</x:t>
+    <x:t>2,800</x:t>
   </x:si>
   <x:si>
     <x:t>Orta Ticarethane</x:t>
@@ -55,13 +55,13 @@
     <x:t>AVM</x:t>
   </x:si>
   <x:si>
-    <x:t>10000</x:t>
+    <x:t>10,000</x:t>
   </x:si>
   <x:si>
     <x:t>Büyük Ticarethane</x:t>
   </x:si>
   <x:si>
-    <x:t>1000</x:t>
+    <x:t>1,000</x:t>
   </x:si>
   <x:si>
     <x:t>0.6</x:t>
@@ -88,7 +88,7 @@
     <x:t>Akaryakıt İstasyonu</x:t>
   </x:si>
   <x:si>
-    <x:t>1400</x:t>
+    <x:t>1,400</x:t>
   </x:si>
   <x:si>
     <x:t>50</x:t>
@@ -124,7 +124,7 @@
     <x:t>Hastane</x:t>
   </x:si>
   <x:si>
-    <x:t>30000</x:t>
+    <x:t>30,000</x:t>
   </x:si>
   <x:si>
     <x:t>0.9</x:t>
@@ -136,7 +136,7 @@
     <x:t>İtfaiye</x:t>
   </x:si>
   <x:si>
-    <x:t>1100</x:t>
+    <x:t>1,100</x:t>
   </x:si>
   <x:si>
     <x:t>60</x:t>
@@ -145,7 +145,7 @@
     <x:t>Kamu Binası</x:t>
   </x:si>
   <x:si>
-    <x:t>1200</x:t>
+    <x:t>1,200</x:t>
   </x:si>
   <x:si>
     <x:t>200</x:t>
@@ -154,7 +154,7 @@
     <x:t>Konser Alanı</x:t>
   </x:si>
   <x:si>
-    <x:t>2000</x:t>
+    <x:t>2,000</x:t>
   </x:si>
   <x:si>
     <x:t>280</x:t>
@@ -163,7 +163,7 @@
     <x:t>Okul</x:t>
   </x:si>
   <x:si>
-    <x:t>7500</x:t>
+    <x:t>7,500</x:t>
   </x:si>
   <x:si>
     <x:t>240</x:t>
@@ -184,7 +184,7 @@
     <x:t>Otogar</x:t>
   </x:si>
   <x:si>
-    <x:t>5800</x:t>
+    <x:t>5,800</x:t>
   </x:si>
   <x:si>
     <x:t>350</x:t>
@@ -196,7 +196,7 @@
     <x:t>Otopark</x:t>
   </x:si>
   <x:si>
-    <x:t>2500</x:t>
+    <x:t>2,500</x:t>
   </x:si>
   <x:si>
     <x:t>160</x:t>
@@ -205,13 +205,13 @@
     <x:t>Pazar Alanı</x:t>
   </x:si>
   <x:si>
-    <x:t>5400</x:t>
+    <x:t>5,400</x:t>
   </x:si>
   <x:si>
     <x:t>PTT</x:t>
   </x:si>
   <x:si>
-    <x:t>Restorant</x:t>
+    <x:t>Restoran</x:t>
   </x:si>
   <x:si>
     <x:t>800</x:t>
@@ -223,13 +223,13 @@
     <x:t>Sanat Alanı</x:t>
   </x:si>
   <x:si>
-    <x:t>3000</x:t>
+    <x:t>3,000</x:t>
   </x:si>
   <x:si>
     <x:t>Sosyal Yaşam Merkezi</x:t>
   </x:si>
   <x:si>
-    <x:t>1500</x:t>
+    <x:t>1,500</x:t>
   </x:si>
   <x:si>
     <x:t>210</x:t>
@@ -238,13 +238,13 @@
     <x:t>Süpermarket</x:t>
   </x:si>
   <x:si>
-    <x:t>3500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Üniversite Kampüs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>200000</x:t>
+    <x:t>3,500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Üniversite Kampüsü</x:t>
+  </x:si>
+  <x:si>
+    <x:t>200,000</x:t>
   </x:si>
 </x:sst>
 </file>
